--- a/보고서/Task작업내용.xlsx
+++ b/보고서/Task작업내용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rudgn\OneDrive\바탕 화면\KDT코드\KDT프로젝트\KDT_Project_1\보고서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9ECEC55F-0D76-428A-BC8B-3BA9FE5BFCB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE346985-5EAB-409D-80E0-F28D9739CA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2745" yWindow="360" windowWidth="21390" windowHeight="15090" xr2:uid="{A35993CA-DE74-4B72-999A-F4799976BF67}"/>
+    <workbookView xWindow="6450" yWindow="345" windowWidth="21390" windowHeight="15090" xr2:uid="{A35993CA-DE74-4B72-999A-F4799976BF67}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
   <si>
     <t>날짜</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -73,6 +73,30 @@
   </si>
   <si>
     <t>점수, 생명력UI, Play 버튼 추가, 인트로화면에서 게임화면 씬변환 구현중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7월 16일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5스테이지 종료시 모달화면으로 점수표시, 점수로직 변경 및 보완</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pause/Replay 기능을 ESC키로 모달상자에 구현 및 공 속도 조절 기능 구현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기존 CSS 보완 및 상호작용 기능 보완</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7월 17일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템구현(생명력회복, 공 위치 초기화)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -122,7 +146,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -182,33 +206,106 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -544,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC8F926-B8D6-45CE-A592-CC34AFA2F8B5}">
-  <dimension ref="B1:D8"/>
+  <dimension ref="B1:D14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.625" customWidth="1"/>
@@ -554,25 +651,25 @@
   <sheetData>
     <row r="1" spans="2:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -580,35 +677,89 @@
       <c r="B6" s="4">
         <v>45488</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="5"/>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
+    <row r="8" spans="2:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="14"/>
+      <c r="C8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="16" t="s">
         <v>9</v>
       </c>
     </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="8"/>
+      <c r="C10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="8"/>
+      <c r="C11" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="6"/>
+      <c r="C13" s="17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="6"/>
+      <c r="C14" s="17" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="B12:B14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/보고서/Task작업내용.xlsx
+++ b/보고서/Task작업내용.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rudgn\OneDrive\바탕 화면\KDT코드\KDT프로젝트\KDT_Project_1\보고서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rudgn\OneDrive\바탕 화면\KDT\KDT프로젝트\KDT_Project_1\보고서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE346985-5EAB-409D-80E0-F28D9739CA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EA91A1-1337-45DE-9D5F-3517947B76F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6450" yWindow="345" windowWidth="21390" windowHeight="15090" xr2:uid="{A35993CA-DE74-4B72-999A-F4799976BF67}"/>
+    <workbookView xWindow="3480" yWindow="330" windowWidth="21390" windowHeight="15090" xr2:uid="{A35993CA-DE74-4B72-999A-F4799976BF67}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>날짜</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -97,6 +97,34 @@
   </si>
   <si>
     <t>아이템구현(생명력회복, 공 위치 초기화)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모서리 충돌시 튕기는 방향 개선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버그 수정 및 코드 보완 / 결과 보고서 기초 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7월 18일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7월 19일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>직접 구현한 기능들의 순서도 작성 및 설명 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점수로직 개선, 종료모달창에 랭킹기능 구현, UI개선, 결과PPT작성 및 순서도 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과 보고서 작성 및 보완</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -146,7 +174,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -207,15 +235,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -249,7 +268,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -259,6 +278,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -268,44 +299,29 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -641,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC8F926-B8D6-45CE-A592-CC34AFA2F8B5}">
-  <dimension ref="B1:D14"/>
+  <dimension ref="B1:D20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.625" customWidth="1"/>
@@ -651,16 +667,16 @@
   <sheetData>
     <row r="1" spans="2:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
@@ -674,7 +690,7 @@
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="4">
+      <c r="B6" s="8">
         <v>45488</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -685,7 +701,7 @@
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="5"/>
+      <c r="B7" s="9"/>
       <c r="C7" s="1" t="s">
         <v>5</v>
       </c>
@@ -694,11 +710,11 @@
       </c>
     </row>
     <row r="8" spans="2:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="14"/>
-      <c r="C8" s="15" t="s">
+      <c r="B8" s="10"/>
+      <c r="C8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -706,60 +722,123 @@
       <c r="B9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="8"/>
-      <c r="C10" s="9" t="s">
+      <c r="B10" s="12"/>
+      <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="8"/>
-      <c r="C11" s="9" t="s">
+      <c r="B11" s="12"/>
+      <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B13" s="6"/>
-      <c r="C13" s="17" t="s">
+      <c r="B13" s="12"/>
+      <c r="C13" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D13" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B14" s="6"/>
-      <c r="C14" s="17" t="s">
+      <c r="B14" s="14"/>
+      <c r="C14" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="D14" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="12"/>
+      <c r="C16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="12"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="12"/>
+      <c r="C17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="12"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="12"/>
+      <c r="C19" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="12"/>
+      <c r="C20" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="B18:B20"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="D15:D17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
